--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXV/LTAIPT_A63F35B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXV/LTAIPT_A63F35B.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -127,31 +127,31 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>ver nota</t>
-  </si>
-  <si>
-    <t>Subdirección Jurídica</t>
-  </si>
-  <si>
-    <t>CB4EC6530AEF331FC952F7741E8F3281</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>04/07/2022</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de abril de 2022 al 30 de junio de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no generó hipervínculo  por alguna recomendación por  casos especiales</t>
+    <t>74757E87F81D451BEE5D85071AC6C19D</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>Subdirección Jurídica.</t>
+  </si>
+  <si>
+    <t>26/07/2023</t>
+  </si>
+  <si>
+    <t>10/01/2023</t>
+  </si>
+  <si>
+    <t>del periodo del 01 de octubre del 2022 al 31 de diciembre del 2022 el colegio de bachilleres del estado de tlaxcala no genero hipervinculopor alguna recomendación por casos especiales.</t>
   </si>
 </sst>
 </file>
@@ -547,7 +547,7 @@
   <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.5703125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.85546875" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -559,7 +559,7 @@
     <col min="10" max="10" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="159.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="157.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
@@ -732,19 +732,19 @@
     </row>
     <row r="8" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>38</v>
@@ -759,10 +759,10 @@
         <v>38</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>44</v>
